--- a/Project Outputs for Jam2M/Jam2M.xlsx
+++ b/Project Outputs for Jam2M/Jam2M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\Jam2M\Project Outputs for Jam2M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6328E297-A3A5-4D1C-965E-DB1655472252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73BA116-A9B3-49F2-B953-EE90F844C5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7230" yWindow="1980" windowWidth="15960" windowHeight="13755" xr2:uid="{7727DCCB-6997-48BF-8E81-5A528886D4AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7727DCCB-6997-48BF-8E81-5A528886D4AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Jam2M" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="134">
   <si>
     <t>Name</t>
   </si>
@@ -417,16 +417,51 @@
   </si>
   <si>
     <t>OLED_0.96IN_WHITE_SSD1306</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005004242324252.html?spm=a2g0o.productlist.main.2.2fa77NCs7NCspd&amp;algo_pvid=9115fd0e-f559-44d5-b0d8-720583a1354c&amp;algo_exp_id=9115fd0e-f559-44d5-b0d8-720583a1354c-1&amp;pdp_ext_f=%7B%22order%22%3A%226097%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%211.95%211.95%21%21%212.23%212.23%21%40211b61bb17787859574283861e9241%2112000056072044330%21sea%21FI%214136394446%21X%211%210%21n_tag%3A-29919%3Bd%3A6ddea204%3Bm03_new_user%3A-29895&amp;curPageLogUid=9py7qZ7cu1tx&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004242324252%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005003042707476.html?spm=a2g0o.productlist.main.14.16781GR01GR0Mt&amp;algo_pvid=097c4793-6c6e-4469-8537-8387a1cbcb5f&amp;algo_exp_id=097c4793-6c6e-4469-8537-8387a1cbcb5f-13&amp;pdp_ext_f=%7B%22order%22%3A%22284%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%212.03%211.99%21%21%212.33%212.28%21%40211b653717783284055801969e934c%2112000023411297177%21sea%21FI%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Abe738c04%3Bm03_new_user%3A-29895&amp;curPageLogUid=zN455cs6qMoh&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005003042707476%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005005496463688.html?spm=a2g0o.cart.0.0.455a38daUqIgZW&amp;mp=1&amp;pdp_npi=6%40dis%21EUR%21EUR+0.64%21EUR+0.48%21%21EUR+0.48%21%21%21%40210398e917787868189693541e1154%2112000046202463475%21ct%21FI%214136394446%21%211%210%21&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22pdpBusinessMode%22%3A%22retail%22%7D%7D</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006141235306.html?spm=a2g0o.productlist.main.1.aaef198bJRB2F5&amp;algo_pvid=5a896666-7ddf-4db0-846b-00101f8e6e8d&amp;algo_exp_id=5a896666-7ddf-4db0-846b-00101f8e6e8d-0&amp;pdp_ext_f=%7B%22order%22%3A%2225440%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%212.59%210.86%21%21%2120.19%216.71%21%40211b80d117783282548952856e08e0%2112000035944225406%21sea%21FI%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Abe738c04%3Bm03_new_user%3A-29895%3BpisId%3A5000000203280146&amp;curPageLogUid=M6nrc8qPDevs&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006141235306%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/32714366180.html?spm=a2g0o.cart.0.0.5dfd38daVh3lII&amp;mp=1&amp;pdp_npi=6%40dis%21EUR%21EUR+0.61%21EUR+0.58%21%21EUR+0.58%21%21%21%40210398e917787870215043654e1154%2161056856324%21ct%21FI%214136394446%21%211%210%21</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005011949752265.html?spm=a2g0o.productlist.main.1.31476l1d6l1dzd&amp;algo_pvid=d5b52a93-6246-4ce3-87d8-b9d7e5b1e4f0&amp;algo_exp_id=d5b52a93-6246-4ce3-87d8-b9d7e5b1e4f0-0&amp;pdp_ext_f=%7B%22order%22%3A%221%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%213.05%213.05%21%21%213.49%213.49%21%40211b655217787871229411007ecec2%2112000057100137937%21sea%21FI%214136394446%21X%211%210%21n_tag%3A-29919%3Bd%3A6ddea204%3Bm03_new_user%3A-29895&amp;curPageLogUid=bTbCUmVmk6Pj&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011949752265%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005010226828145.html?spm=a2g0o.cart.0.0.1c6c38dao4t1EB&amp;mp=1&amp;pdp_npi=6%40dis%21EUR%21EUR+1.07%21EUR+1.02%21%21EUR+1.02%21%21%21%40210398e917787872847355901e1154%2112000051594837693%21ct%21FI%214136394446%21%212%210%21</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008743194888.html?spm=a2g0o.productlist.main.3.44f467b9na73UZ&amp;algo_pvid=eaa24f7c-fe49-4501-94ce-b2f96b2b0555&amp;algo_exp_id=eaa24f7c-fe49-4501-94ce-b2f96b2b0555-2&amp;pdp_ext_f=%7B%22order%22%3A%221%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%213.73%213.70%21%21%214.27%214.23%21%40211b628117787873357451283e7ce9%2112000046485062129%21sea%21FI%214136394446%21X%211%210%21n_tag%3A-29919%3Bd%3A6ddea204%3Bm03_new_user%3A-29895&amp;curPageLogUid=5TB59cmfscb0&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008743194888%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005006257173539.html?spm=a2g0o.productlist.main.24.40fa15d9cAXVvp&amp;algo_pvid=3e01e0e8-4eb5-4c11-9d2c-f36790b5f0f7&amp;algo_exp_id=3e01e0e8-4eb5-4c11-9d2c-f36790b5f0f7-35&amp;pdp_ext_f=%7B%22order%22%3A%22881%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%212.44%212.44%21%21%2118.96%2118.96%21%40211b6c1917787875754881141e8499%2112000036496181522%21sea%21FI%214136394446%21X%211%210%21n_tag%3A-29919%3Bd%3A6ddea204%3Bm03_new_user%3A-29895&amp;curPageLogUid=HJiAp68Wf0Zn&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006257173539%7C_p_origin_prod%3A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -446,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -469,18 +504,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -813,13 +863,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{270D6383-6C66-41BF-96DB-464059782BD7}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" customWidth="1"/>
+    <col min="3" max="6" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -839,7 +891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -858,8 +910,11 @@
       <c r="F2" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -877,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -897,7 +952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -917,7 +972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -937,7 +992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -957,7 +1012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
@@ -977,7 +1032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -997,7 +1052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -1017,7 +1072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1037,7 +1092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -1057,7 +1112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -1076,8 +1131,11 @@
       <c r="F13" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>56</v>
       </c>
@@ -1096,8 +1154,11 @@
       <c r="F14" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
@@ -1117,7 +1178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>64</v>
       </c>
@@ -1137,7 +1198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>69</v>
       </c>
@@ -1157,7 +1218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>73</v>
       </c>
@@ -1177,7 +1238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>77</v>
       </c>
@@ -1197,7 +1258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>81</v>
       </c>
@@ -1217,7 +1278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>85</v>
       </c>
@@ -1237,7 +1298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>89</v>
       </c>
@@ -1257,7 +1318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>93</v>
       </c>
@@ -1277,7 +1338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>97</v>
       </c>
@@ -1297,7 +1358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>100</v>
       </c>
@@ -1316,8 +1377,11 @@
       <c r="F25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>104</v>
       </c>
@@ -1336,8 +1400,11 @@
       <c r="F26" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>108</v>
       </c>
@@ -1356,8 +1423,11 @@
       <c r="F27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>112</v>
       </c>
@@ -1376,8 +1446,11 @@
       <c r="F28" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>117</v>
       </c>
@@ -1396,8 +1469,11 @@
       <c r="F29" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>121</v>
       </c>
@@ -1416,9 +1492,17 @@
       <c r="F30" s="1">
         <v>1</v>
       </c>
+      <c r="G30" s="5" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.aliexpress.com/item/1005005496463688.html?spm=a2g0o.cart.0.0.455a38daUqIgZW&amp;mp=1&amp;pdp_npi=6%40dis%21EUR%21EUR+0.64%21EUR+0.48%21%21EUR+0.48%21%21%21%40210398e917787868189693541e1154%2112000046202463475%21ct%21FI%214136394446%21%211%210%21&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22pdpBusinessMode%22%3A%22retail%22%7D%7D" xr:uid="{B398F3B1-B61B-4E04-AC97-E2D9B608FB6A}"/>
+    <hyperlink ref="G27" r:id="rId2" xr:uid="{79ECEBD0-BACB-45EE-8928-86E1CBB638CD}"/>
+    <hyperlink ref="G26" r:id="rId3" xr:uid="{B420BD88-CF9B-470F-8080-D29EFE584D0E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>